--- a/eng-w26.xlsx
+++ b/eng-w26.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kenlo\Desktop\2526_Winter_SFQ_Data\File Upload to AQA website\Regen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B1122DD-EA45-439F-AB42-3418F77D557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{0B1122DD-EA45-439F-AB42-3418F77D557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCF7FE4-5541-4FFA-824F-44889820C231}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{C0B00039-309F-45EC-AD76-51F5EBD3E9D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C0B00039-309F-45EC-AD76-51F5EBD3E9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="School_Term_Summary_Report-SENG" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="86">
   <si>
     <t>Academic Year</t>
   </si>
@@ -73,34 +73,19 @@
     <t>Low Response Rate Indicator</t>
   </si>
   <si>
-    <t>Response Rate (Adjusted)</t>
-  </si>
-  <si>
     <t>No. of Sections Evaluated</t>
   </si>
   <si>
     <t>Course Overall - Mean</t>
   </si>
   <si>
-    <t>Course Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Course Overall - SD</t>
   </si>
   <si>
-    <t>Course Overall - SD (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - Mean</t>
   </si>
   <si>
-    <t>Instructor Overall - Mean (Adjusted)</t>
-  </si>
-  <si>
     <t>Instructor Overall - SD</t>
-  </si>
-  <si>
-    <t>Instructor Overall - SD (Adjusted)</t>
   </si>
   <si>
     <t>25-26</t>
@@ -1155,10 +1140,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB84637-EB23-4782-BDBD-D84114491C76}">
-  <dimension ref="A1:AA46"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1225,463 +1210,448 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>28</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.253</v>
       </c>
       <c r="Q2" t="s">
-        <v>30</v>
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>9</v>
       </c>
       <c r="S2">
-        <v>9</v>
+        <v>4.12</v>
       </c>
       <c r="T2">
-        <v>4.12</v>
+        <v>0.88</v>
+      </c>
+      <c r="U2">
+        <v>3.99</v>
       </c>
       <c r="V2">
-        <v>0.88</v>
-      </c>
-      <c r="X2">
-        <v>3.99</v>
-      </c>
-      <c r="Z2">
         <v>0.91</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
       <c r="F3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.127</v>
       </c>
       <c r="Q3" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>3.78</v>
       </c>
       <c r="T3">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U3">
+        <v>3.94</v>
       </c>
       <c r="V3">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X3">
-        <v>3.94</v>
-      </c>
-      <c r="Z3">
         <v>0.88</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
       <c r="F4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.29199999999999998</v>
       </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
       <c r="S4">
-        <v>5</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="T4">
-        <v>4.2300000000000004</v>
+        <v>0.66</v>
+      </c>
+      <c r="U4">
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>0.66</v>
-      </c>
-      <c r="X4">
-        <v>4</v>
-      </c>
-      <c r="Z4">
         <v>0.82</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>1</v>
       </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
       <c r="S5">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U5">
         <v>4.67</v>
       </c>
       <c r="V5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="X5">
-        <v>4.67</v>
-      </c>
-      <c r="Z5">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
       <c r="F6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.69199999999999995</v>
       </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
       <c r="S6">
-        <v>2</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="T6">
-        <v>4.1900000000000004</v>
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>3.96</v>
       </c>
       <c r="V6">
-        <v>1</v>
-      </c>
-      <c r="X6">
-        <v>3.96</v>
-      </c>
-      <c r="Z6">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>2020</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1">
         <v>0.127</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>3.78</v>
       </c>
       <c r="T7">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U7">
+        <v>3.94</v>
       </c>
       <c r="V7">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X7">
-        <v>3.94</v>
-      </c>
-      <c r="Z7">
         <v>0.88</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>2020</v>
       </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O8">
         <v>213</v>
@@ -1690,66 +1660,66 @@
         <v>0.127</v>
       </c>
       <c r="Q8" t="s">
-        <v>33</v>
-      </c>
-      <c r="S8" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <v>3.78</v>
       </c>
       <c r="T8">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U8">
+        <v>3.94</v>
       </c>
       <c r="V8">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X8">
-        <v>3.94</v>
-      </c>
-      <c r="Z8">
         <v>0.88</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>2020</v>
       </c>
       <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s">
         <v>39</v>
-      </c>
-      <c r="I9" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" t="s">
-        <v>44</v>
       </c>
       <c r="O9">
         <v>213</v>
@@ -1758,66 +1728,66 @@
         <v>0.127</v>
       </c>
       <c r="Q9" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9">
+        <v>3.78</v>
       </c>
       <c r="T9">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U9">
+        <v>3.89</v>
       </c>
       <c r="V9">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X9">
-        <v>3.89</v>
-      </c>
-      <c r="Z9">
         <v>1.01</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" t="s">
         <v>27</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" t="s">
-        <v>32</v>
-      </c>
       <c r="F10" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>2020</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J10" t="s">
+        <v>35</v>
+      </c>
+      <c r="K10" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
         <v>40</v>
       </c>
-      <c r="K10" t="s">
-        <v>30</v>
-      </c>
-      <c r="L10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" t="s">
-        <v>45</v>
-      </c>
       <c r="N10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="O10">
         <v>213</v>
@@ -1826,134 +1796,134 @@
         <v>0.127</v>
       </c>
       <c r="Q10" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>3.78</v>
       </c>
       <c r="T10">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
       </c>
       <c r="V10">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="X10">
-        <v>4</v>
-      </c>
-      <c r="Z10">
         <v>0.73</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
       <c r="F11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G11">
         <v>1028</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1">
         <v>0.30599999999999999</v>
       </c>
       <c r="Q11" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>4.07</v>
       </c>
       <c r="T11">
-        <v>4.07</v>
+        <v>0.7</v>
+      </c>
+      <c r="U11">
+        <v>3.87</v>
       </c>
       <c r="V11">
-        <v>0.7</v>
-      </c>
-      <c r="X11">
-        <v>3.87</v>
-      </c>
-      <c r="Z11">
         <v>0.92</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="E12" t="s">
-        <v>34</v>
-      </c>
       <c r="F12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>1028</v>
       </c>
       <c r="H12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="K12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O12">
         <v>49</v>
@@ -1962,66 +1932,66 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q12" t="s">
-        <v>33</v>
-      </c>
-      <c r="S12" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12">
+        <v>4.07</v>
       </c>
       <c r="T12">
-        <v>4.07</v>
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>3.87</v>
       </c>
       <c r="V12">
-        <v>0.7</v>
-      </c>
-      <c r="X12">
-        <v>3.87</v>
-      </c>
-      <c r="Z12">
         <v>0.92</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="E13" t="s">
-        <v>34</v>
-      </c>
       <c r="F13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>1028</v>
       </c>
       <c r="H13" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" t="s">
+        <v>44</v>
+      </c>
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
+        <v>45</v>
+      </c>
+      <c r="M13" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" t="s">
         <v>47</v>
-      </c>
-      <c r="J13" t="s">
-        <v>49</v>
-      </c>
-      <c r="K13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L13" t="s">
-        <v>50</v>
-      </c>
-      <c r="M13" t="s">
-        <v>51</v>
-      </c>
-      <c r="N13" t="s">
-        <v>52</v>
       </c>
       <c r="O13">
         <v>49</v>
@@ -2030,134 +2000,134 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q13" t="s">
-        <v>33</v>
-      </c>
-      <c r="S13" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>4.07</v>
       </c>
       <c r="T13">
-        <v>4.07</v>
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>3.87</v>
       </c>
       <c r="V13">
-        <v>0.7</v>
-      </c>
-      <c r="X13">
-        <v>3.87</v>
-      </c>
-      <c r="Z13">
         <v>0.92</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
       <c r="F14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1">
         <v>0.34</v>
       </c>
       <c r="Q14" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>4.47</v>
       </c>
       <c r="T14">
-        <v>4.47</v>
+        <v>0.72</v>
+      </c>
+      <c r="U14">
+        <v>4.12</v>
       </c>
       <c r="V14">
-        <v>0.72</v>
-      </c>
-      <c r="X14">
-        <v>4.12</v>
-      </c>
-      <c r="Z14">
         <v>0.86</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" t="s">
         <v>29</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" t="s">
         <v>34</v>
       </c>
-      <c r="F15" t="s">
-        <v>34</v>
-      </c>
-      <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>39</v>
-      </c>
       <c r="I15" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J15" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O15">
         <v>50</v>
@@ -2166,66 +2136,66 @@
         <v>0.34</v>
       </c>
       <c r="Q15" t="s">
-        <v>33</v>
-      </c>
-      <c r="S15" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15">
+        <v>4.47</v>
       </c>
       <c r="T15">
-        <v>4.47</v>
+        <v>0.72</v>
+      </c>
+      <c r="U15">
+        <v>4.12</v>
       </c>
       <c r="V15">
-        <v>0.72</v>
-      </c>
-      <c r="X15">
-        <v>4.12</v>
-      </c>
-      <c r="Z15">
         <v>0.86</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>29</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
         <v>34</v>
       </c>
-      <c r="F16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" t="s">
-        <v>53</v>
-      </c>
-      <c r="H16" t="s">
-        <v>39</v>
-      </c>
       <c r="I16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="J16" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="K16" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L16" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N16" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O16">
         <v>50</v>
@@ -2234,134 +2204,134 @@
         <v>0.34</v>
       </c>
       <c r="Q16" t="s">
-        <v>33</v>
-      </c>
-      <c r="S16" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.47</v>
       </c>
       <c r="T16">
-        <v>4.47</v>
+        <v>0.72</v>
+      </c>
+      <c r="U16">
+        <v>4.12</v>
       </c>
       <c r="V16">
-        <v>0.72</v>
-      </c>
-      <c r="X16">
-        <v>4.12</v>
-      </c>
-      <c r="Z16">
         <v>0.86</v>
       </c>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="E17" t="s">
-        <v>34</v>
-      </c>
       <c r="F17" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1">
         <v>0.33300000000000002</v>
       </c>
       <c r="Q17" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="T17">
-        <v>4.2699999999999996</v>
+        <v>0.59</v>
+      </c>
+      <c r="U17">
+        <v>3.93</v>
       </c>
       <c r="V17">
-        <v>0.59</v>
-      </c>
-      <c r="X17">
-        <v>3.93</v>
-      </c>
-      <c r="Z17">
         <v>0.88</v>
       </c>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" t="s">
         <v>29</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
         <v>34</v>
       </c>
-      <c r="F18" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" t="s">
-        <v>39</v>
-      </c>
       <c r="I18" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J18" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O18">
         <v>45</v>
@@ -2370,66 +2340,66 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q18" t="s">
-        <v>33</v>
-      </c>
-      <c r="S18" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18">
+        <v>4.2699999999999996</v>
       </c>
       <c r="T18">
-        <v>4.2699999999999996</v>
+        <v>0.59</v>
+      </c>
+      <c r="U18">
+        <v>3.93</v>
       </c>
       <c r="V18">
-        <v>0.59</v>
-      </c>
-      <c r="X18">
-        <v>3.93</v>
-      </c>
-      <c r="Z18">
         <v>0.88</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
         <v>34</v>
       </c>
-      <c r="F19" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" t="s">
-        <v>57</v>
-      </c>
-      <c r="H19" t="s">
-        <v>39</v>
-      </c>
       <c r="I19" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="J19" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K19" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L19" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N19" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O19">
         <v>45</v>
@@ -2438,134 +2408,134 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q19" t="s">
-        <v>33</v>
-      </c>
-      <c r="S19" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19">
+        <v>4.2699999999999996</v>
       </c>
       <c r="T19">
-        <v>4.2699999999999996</v>
+        <v>0.59</v>
+      </c>
+      <c r="U19">
+        <v>3.93</v>
       </c>
       <c r="V19">
-        <v>0.59</v>
-      </c>
-      <c r="X19">
-        <v>3.93</v>
-      </c>
-      <c r="Z19">
         <v>0.88</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
         <v>29</v>
       </c>
-      <c r="E20" t="s">
-        <v>34</v>
-      </c>
       <c r="F20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O20" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1">
         <v>0.2</v>
       </c>
       <c r="Q20" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>5</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
-      <c r="X20">
-        <v>5</v>
-      </c>
-      <c r="Z20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" t="s">
         <v>29</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
+        <v>29</v>
+      </c>
+      <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
         <v>34</v>
       </c>
-      <c r="F21" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" t="s">
-        <v>61</v>
-      </c>
-      <c r="H21" t="s">
-        <v>39</v>
-      </c>
       <c r="I21" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2574,66 +2544,66 @@
         <v>0.2</v>
       </c>
       <c r="Q21" t="s">
-        <v>33</v>
-      </c>
-      <c r="S21" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R21" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21">
+        <v>4</v>
       </c>
       <c r="T21">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
-      <c r="X21">
-        <v>5</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" t="s">
         <v>34</v>
       </c>
-      <c r="F22" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" t="s">
-        <v>39</v>
-      </c>
       <c r="I22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="J22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K22" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L22" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="M22" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N22" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2642,134 +2612,134 @@
         <v>0.2</v>
       </c>
       <c r="Q22" t="s">
-        <v>33</v>
-      </c>
-      <c r="S22" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22">
+        <v>4</v>
       </c>
       <c r="T22">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>5</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
-      <c r="X22">
-        <v>5</v>
-      </c>
-      <c r="Z22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
         <v>29</v>
       </c>
-      <c r="E23" t="s">
-        <v>34</v>
-      </c>
       <c r="F23" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I23" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O23" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P23" s="1">
         <v>0.19600000000000001</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23">
+        <v>0.5</v>
+      </c>
+      <c r="U23">
         <v>4</v>
       </c>
       <c r="V23">
         <v>0.5</v>
       </c>
-      <c r="X23">
-        <v>4</v>
-      </c>
-      <c r="Z23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" t="s">
         <v>29</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
         <v>34</v>
       </c>
-      <c r="F24" t="s">
-        <v>34</v>
-      </c>
-      <c r="G24" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" t="s">
-        <v>39</v>
-      </c>
       <c r="I24" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J24" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O24">
         <v>46</v>
@@ -2778,66 +2748,66 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q24" t="s">
-        <v>33</v>
-      </c>
-      <c r="S24" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R24" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24">
+        <v>4</v>
       </c>
       <c r="T24">
+        <v>0.5</v>
+      </c>
+      <c r="U24">
         <v>4</v>
       </c>
       <c r="V24">
         <v>0.5</v>
       </c>
-      <c r="X24">
-        <v>4</v>
-      </c>
-      <c r="Z24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
         <v>29</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" t="s">
         <v>34</v>
       </c>
-      <c r="F25" t="s">
-        <v>34</v>
-      </c>
-      <c r="G25" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" t="s">
-        <v>39</v>
-      </c>
       <c r="I25" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J25" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="K25" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L25" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M25" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="N25" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="O25">
         <v>46</v>
@@ -2846,131 +2816,131 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q25" t="s">
-        <v>33</v>
-      </c>
-      <c r="S25" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25">
+        <v>4</v>
       </c>
       <c r="T25">
+        <v>0.5</v>
+      </c>
+      <c r="U25">
         <v>4</v>
       </c>
       <c r="V25">
         <v>0.5</v>
       </c>
-      <c r="X25">
-        <v>4</v>
-      </c>
-      <c r="Z25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D26" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O26" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P26" s="1">
         <v>1</v>
       </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
       <c r="S26">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T26">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U26">
         <v>4.67</v>
       </c>
       <c r="V26">
         <v>0.57999999999999996</v>
       </c>
-      <c r="X26">
-        <v>4.67</v>
-      </c>
-      <c r="Z26">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="H27" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J27" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -2978,64 +2948,64 @@
       <c r="P27" s="1">
         <v>1</v>
       </c>
-      <c r="S27" t="s">
-        <v>30</v>
+      <c r="R27" t="s">
+        <v>25</v>
+      </c>
+      <c r="S27">
+        <v>4.67</v>
       </c>
       <c r="T27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U27">
         <v>4.67</v>
       </c>
       <c r="V27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="X27">
-        <v>4.67</v>
-      </c>
-      <c r="Z27">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" t="s">
+        <v>65</v>
+      </c>
+      <c r="J28" t="s">
+        <v>67</v>
+      </c>
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" t="s">
         <v>69</v>
       </c>
-      <c r="H28" t="s">
-        <v>71</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="N28" t="s">
         <v>70</v>
-      </c>
-      <c r="J28" t="s">
-        <v>72</v>
-      </c>
-      <c r="K28" t="s">
-        <v>30</v>
-      </c>
-      <c r="L28" t="s">
-        <v>73</v>
-      </c>
-      <c r="M28" t="s">
-        <v>74</v>
-      </c>
-      <c r="N28" t="s">
-        <v>75</v>
       </c>
       <c r="O28">
         <v>3</v>
@@ -3043,132 +3013,132 @@
       <c r="P28" s="1">
         <v>1</v>
       </c>
-      <c r="S28" t="s">
-        <v>30</v>
+      <c r="R28" t="s">
+        <v>25</v>
+      </c>
+      <c r="S28">
+        <v>4.67</v>
       </c>
       <c r="T28">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U28">
         <v>4.67</v>
       </c>
       <c r="V28">
         <v>0.57999999999999996</v>
       </c>
-      <c r="X28">
-        <v>4.67</v>
-      </c>
-      <c r="Z28">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G29">
         <v>1900</v>
       </c>
       <c r="H29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O29" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P29" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q29" t="s">
-        <v>33</v>
+        <v>28</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="T29">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
+      </c>
+      <c r="U29">
+        <v>3.73</v>
       </c>
       <c r="V29">
-        <v>1.03</v>
-      </c>
-      <c r="X29">
-        <v>3.73</v>
-      </c>
-      <c r="Z29">
         <v>1.27</v>
       </c>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G30">
         <v>1900</v>
       </c>
       <c r="H30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O30">
         <v>20</v>
@@ -3177,66 +3147,66 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q30" t="s">
-        <v>33</v>
-      </c>
-      <c r="S30" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R30" t="s">
+        <v>25</v>
+      </c>
+      <c r="S30">
+        <v>4.3600000000000003</v>
       </c>
       <c r="T30">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
+      </c>
+      <c r="U30">
+        <v>3.73</v>
       </c>
       <c r="V30">
-        <v>1.03</v>
-      </c>
-      <c r="X30">
-        <v>3.73</v>
-      </c>
-      <c r="Z30">
         <v>1.27</v>
       </c>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G31">
         <v>1900</v>
       </c>
       <c r="H31" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="J31" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="K31" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N31" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O31">
         <v>20</v>
@@ -3245,131 +3215,131 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q31" t="s">
-        <v>33</v>
-      </c>
-      <c r="S31" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="R31" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31">
+        <v>4.3600000000000003</v>
       </c>
       <c r="T31">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
+      </c>
+      <c r="U31">
+        <v>3.73</v>
       </c>
       <c r="V31">
-        <v>1.03</v>
-      </c>
-      <c r="X31">
-        <v>3.73</v>
-      </c>
-      <c r="Z31">
         <v>1.27</v>
       </c>
     </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D32" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I32" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P32" s="1">
         <v>0.84199999999999997</v>
       </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
       <c r="S32">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="T32">
         <v>1</v>
       </c>
-      <c r="T32">
-        <v>4.0599999999999996</v>
+      <c r="U32">
+        <v>4.13</v>
       </c>
       <c r="V32">
-        <v>1</v>
-      </c>
-      <c r="X32">
-        <v>4.13</v>
-      </c>
-      <c r="Z32">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I33" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J33" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="O33">
         <v>19</v>
@@ -3377,64 +3347,64 @@
       <c r="P33" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="S33" t="s">
-        <v>30</v>
+      <c r="R33" t="s">
+        <v>25</v>
+      </c>
+      <c r="S33">
+        <v>4.0599999999999996</v>
       </c>
       <c r="T33">
-        <v>4.0599999999999996</v>
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>4.13</v>
       </c>
       <c r="V33">
-        <v>1</v>
-      </c>
-      <c r="X33">
-        <v>4.13</v>
-      </c>
-      <c r="Z33">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C34" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="H34" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I34" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J34" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K34" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L34" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="M34" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="N34" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="O34">
         <v>19</v>
@@ -3442,63 +3412,63 @@
       <c r="P34" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="S34" t="s">
-        <v>30</v>
+      <c r="R34" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34">
+        <v>4.0599999999999996</v>
       </c>
       <c r="T34">
-        <v>4.0599999999999996</v>
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>4.13</v>
       </c>
       <c r="V34">
-        <v>1</v>
-      </c>
-      <c r="X34">
-        <v>4.13</v>
-      </c>
-      <c r="Z34">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46082</v>
       </c>
@@ -3509,6 +3479,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -3757,15 +3736,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3778,13 +3748,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC5CE1B-1BD6-4316-80DD-7CA3CEA4748B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85228DDE-C556-480B-A8EE-634E9DB6BA7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85228DDE-C556-480B-A8EE-634E9DB6BA7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC5CE1B-1BD6-4316-80DD-7CA3CEA4748B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62F3A27C-5630-4178-BF85-500E1091F759}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62F3A27C-5630-4178-BF85-500E1091F759}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="307c76f0-d205-4835-9aae-d70c69349486"/>
+    <ds:schemaRef ds:uri="c1544048-3019-4d62-a7f3-2ad0cae9f9e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/eng-w26.xlsx
+++ b/eng-w26.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_New/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{0B1122DD-EA45-439F-AB42-3418F77D557A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACCF7FE4-5541-4FFA-824F-44889820C231}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{5A99AFDF-7AF1-4818-B417-3385FD53B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3789758-9D48-4B29-B4C6-5DED05DD84D0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C0B00039-309F-45EC-AD76-51F5EBD3E9D0}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C2C8D75B-5B47-4BFF-BBF0-E60AFD6116EA}"/>
   </bookViews>
   <sheets>
-    <sheet name="School_Term_Summary_Report-SENG" sheetId="1" r:id="rId1"/>
+    <sheet name="eng-w26" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="87">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
+  </si>
+  <si>
+    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1139,11 +1142,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFB84637-EB23-4782-BDBD-D84114491C76}">
-  <dimension ref="A1:V46"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4966C0D6-3632-473C-9624-470A15F4ED59}">
+  <dimension ref="A1:W46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1210,448 +1213,451 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P2" s="1">
         <v>0.253</v>
       </c>
       <c r="Q2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2">
+        <v>9</v>
+      </c>
+      <c r="T2">
+        <v>4.12</v>
+      </c>
+      <c r="U2">
+        <v>0.88</v>
+      </c>
+      <c r="V2">
+        <v>3.99</v>
+      </c>
+      <c r="W2">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
         <v>25</v>
       </c>
-      <c r="R2">
-        <v>9</v>
-      </c>
-      <c r="S2">
-        <v>4.12</v>
-      </c>
-      <c r="T2">
-        <v>0.88</v>
-      </c>
-      <c r="U2">
-        <v>3.99</v>
-      </c>
-      <c r="V2">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P3" s="1">
         <v>0.127</v>
       </c>
       <c r="Q3" t="s">
-        <v>28</v>
-      </c>
-      <c r="R3">
+        <v>29</v>
+      </c>
+      <c r="S3">
         <v>1</v>
       </c>
-      <c r="S3">
+      <c r="T3">
         <v>3.78</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>3.94</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>0.88</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4" s="1">
         <v>0.29199999999999998</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="S4">
+      <c r="T4">
         <v>4.2300000000000004</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <v>0.66</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>4</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>0.82</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P5" s="1">
         <v>1</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>1</v>
       </c>
-      <c r="S5">
+      <c r="T5">
         <v>4.67</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>4.67</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P6" s="1">
         <v>0.69199999999999995</v>
       </c>
-      <c r="R6">
+      <c r="S6">
         <v>2</v>
       </c>
-      <c r="S6">
+      <c r="T6">
         <v>4.1900000000000004</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <v>1</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>3.96</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
         <v>2020</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P7" s="1">
         <v>0.127</v>
       </c>
       <c r="Q7" t="s">
-        <v>28</v>
-      </c>
-      <c r="R7">
+        <v>29</v>
+      </c>
+      <c r="S7">
         <v>1</v>
       </c>
-      <c r="S7">
+      <c r="T7">
         <v>3.78</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <v>1.1200000000000001</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>3.94</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>0.88</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8">
         <v>2020</v>
       </c>
       <c r="H8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I8" t="s">
         <v>34</v>
       </c>
-      <c r="I8" t="s">
-        <v>33</v>
-      </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O8">
         <v>213</v>
@@ -1660,66 +1666,66 @@
         <v>0.127</v>
       </c>
       <c r="Q8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8" t="s">
+        <v>26</v>
+      </c>
+      <c r="T8">
+        <v>3.78</v>
+      </c>
+      <c r="U8">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="V8">
+        <v>3.94</v>
+      </c>
+      <c r="W8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="R8" t="s">
-        <v>25</v>
-      </c>
-      <c r="S8">
-        <v>3.78</v>
-      </c>
-      <c r="T8">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="U8">
-        <v>3.94</v>
-      </c>
-      <c r="V8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E9" t="s">
-        <v>27</v>
-      </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G9">
         <v>2020</v>
       </c>
       <c r="H9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I9" t="s">
         <v>34</v>
       </c>
-      <c r="I9" t="s">
-        <v>33</v>
-      </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O9">
         <v>213</v>
@@ -1728,66 +1734,66 @@
         <v>0.127</v>
       </c>
       <c r="Q9" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9" t="s">
+        <v>26</v>
+      </c>
+      <c r="T9">
+        <v>3.78</v>
+      </c>
+      <c r="U9">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="V9">
+        <v>3.89</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" t="s">
         <v>28</v>
       </c>
-      <c r="R9" t="s">
-        <v>25</v>
-      </c>
-      <c r="S9">
-        <v>3.78</v>
-      </c>
-      <c r="T9">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="U9">
-        <v>3.89</v>
-      </c>
-      <c r="V9">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" t="s">
-        <v>27</v>
-      </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G10">
         <v>2020</v>
       </c>
       <c r="H10" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" t="s">
         <v>34</v>
       </c>
-      <c r="I10" t="s">
-        <v>33</v>
-      </c>
       <c r="J10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O10">
         <v>213</v>
@@ -1796,134 +1802,134 @@
         <v>0.127</v>
       </c>
       <c r="Q10" t="s">
-        <v>28</v>
-      </c>
-      <c r="R10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10" t="s">
+        <v>26</v>
+      </c>
+      <c r="T10">
+        <v>3.78</v>
+      </c>
+      <c r="U10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="V10">
+        <v>4</v>
+      </c>
+      <c r="W10">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="S10">
-        <v>3.78</v>
-      </c>
-      <c r="T10">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="U10">
-        <v>4</v>
-      </c>
-      <c r="V10">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
-      </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G11">
         <v>1028</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P11" s="1">
         <v>0.30599999999999999</v>
       </c>
       <c r="Q11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11">
+        <v>29</v>
+      </c>
+      <c r="S11">
         <v>1</v>
       </c>
-      <c r="S11">
+      <c r="T11">
         <v>4.07</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <v>0.7</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>3.87</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>0.92</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>1028</v>
       </c>
       <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
         <v>43</v>
       </c>
-      <c r="I12" t="s">
-        <v>42</v>
-      </c>
       <c r="J12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O12">
         <v>49</v>
@@ -1932,66 +1938,66 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q12" t="s">
-        <v>28</v>
-      </c>
-      <c r="R12" t="s">
+        <v>29</v>
+      </c>
+      <c r="S12" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12">
+        <v>4.07</v>
+      </c>
+      <c r="U12">
+        <v>0.7</v>
+      </c>
+      <c r="V12">
+        <v>3.87</v>
+      </c>
+      <c r="W12">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" t="s">
         <v>25</v>
       </c>
-      <c r="S12">
-        <v>4.07</v>
-      </c>
-      <c r="T12">
-        <v>0.7</v>
-      </c>
-      <c r="U12">
-        <v>3.87</v>
-      </c>
-      <c r="V12">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" t="s">
-        <v>24</v>
-      </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>1028</v>
       </c>
       <c r="H13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
         <v>43</v>
       </c>
-      <c r="I13" t="s">
-        <v>42</v>
-      </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O13">
         <v>49</v>
@@ -2000,134 +2006,134 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q13" t="s">
-        <v>28</v>
-      </c>
-      <c r="R13" t="s">
+        <v>29</v>
+      </c>
+      <c r="S13" t="s">
+        <v>26</v>
+      </c>
+      <c r="T13">
+        <v>4.07</v>
+      </c>
+      <c r="U13">
+        <v>0.7</v>
+      </c>
+      <c r="V13">
+        <v>3.87</v>
+      </c>
+      <c r="W13">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
         <v>25</v>
       </c>
-      <c r="S13">
-        <v>4.07</v>
-      </c>
-      <c r="T13">
-        <v>0.7</v>
-      </c>
-      <c r="U13">
-        <v>3.87</v>
-      </c>
-      <c r="V13">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
-        <v>24</v>
-      </c>
       <c r="E14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P14" s="1">
         <v>0.34</v>
       </c>
       <c r="Q14" t="s">
-        <v>28</v>
-      </c>
-      <c r="R14">
+        <v>29</v>
+      </c>
+      <c r="S14">
         <v>1</v>
       </c>
-      <c r="S14">
+      <c r="T14">
         <v>4.47</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <v>0.72</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>4.12</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>0.86</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N15" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O15">
         <v>50</v>
@@ -2136,66 +2142,66 @@
         <v>0.34</v>
       </c>
       <c r="Q15" t="s">
-        <v>28</v>
-      </c>
-      <c r="R15" t="s">
+        <v>29</v>
+      </c>
+      <c r="S15" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15">
+        <v>4.47</v>
+      </c>
+      <c r="U15">
+        <v>0.72</v>
+      </c>
+      <c r="V15">
+        <v>4.12</v>
+      </c>
+      <c r="W15">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
         <v>25</v>
       </c>
-      <c r="S15">
-        <v>4.47</v>
-      </c>
-      <c r="T15">
-        <v>0.72</v>
-      </c>
-      <c r="U15">
-        <v>4.12</v>
-      </c>
-      <c r="V15">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" t="s">
+        <v>50</v>
+      </c>
+      <c r="J16" t="s">
+        <v>51</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>52</v>
+      </c>
+      <c r="M16" t="s">
+        <v>47</v>
+      </c>
+      <c r="N16" t="s">
         <v>48</v>
-      </c>
-      <c r="H16" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" t="s">
-        <v>49</v>
-      </c>
-      <c r="J16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K16" t="s">
-        <v>25</v>
-      </c>
-      <c r="L16" t="s">
-        <v>51</v>
-      </c>
-      <c r="M16" t="s">
-        <v>46</v>
-      </c>
-      <c r="N16" t="s">
-        <v>47</v>
       </c>
       <c r="O16">
         <v>50</v>
@@ -2204,134 +2210,134 @@
         <v>0.34</v>
       </c>
       <c r="Q16" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" t="s">
+        <v>29</v>
+      </c>
+      <c r="S16" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16">
+        <v>4.47</v>
+      </c>
+      <c r="U16">
+        <v>0.72</v>
+      </c>
+      <c r="V16">
+        <v>4.12</v>
+      </c>
+      <c r="W16">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" t="s">
         <v>25</v>
       </c>
-      <c r="S16">
-        <v>4.47</v>
-      </c>
-      <c r="T16">
-        <v>0.72</v>
-      </c>
-      <c r="U16">
-        <v>4.12</v>
-      </c>
-      <c r="V16">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>24</v>
-      </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P17" s="1">
         <v>0.33300000000000002</v>
       </c>
       <c r="Q17" t="s">
-        <v>28</v>
-      </c>
-      <c r="R17">
+        <v>29</v>
+      </c>
+      <c r="S17">
         <v>1</v>
       </c>
-      <c r="S17">
+      <c r="T17">
         <v>4.2699999999999996</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <v>0.59</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>3.93</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>0.88</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H18" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I18" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J18" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O18">
         <v>45</v>
@@ -2340,66 +2346,66 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q18" t="s">
-        <v>28</v>
-      </c>
-      <c r="R18" t="s">
+        <v>29</v>
+      </c>
+      <c r="S18" t="s">
+        <v>26</v>
+      </c>
+      <c r="T18">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U18">
+        <v>0.59</v>
+      </c>
+      <c r="V18">
+        <v>3.93</v>
+      </c>
+      <c r="W18">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" t="s">
         <v>25</v>
       </c>
-      <c r="S18">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="T18">
-        <v>0.59</v>
-      </c>
-      <c r="U18">
-        <v>3.93</v>
-      </c>
-      <c r="V18">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O19">
         <v>45</v>
@@ -2408,134 +2414,134 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
-      </c>
-      <c r="R19" t="s">
+        <v>29</v>
+      </c>
+      <c r="S19" t="s">
+        <v>26</v>
+      </c>
+      <c r="T19">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="U19">
+        <v>0.59</v>
+      </c>
+      <c r="V19">
+        <v>3.93</v>
+      </c>
+      <c r="W19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" t="s">
         <v>25</v>
       </c>
-      <c r="S19">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="T19">
-        <v>0.59</v>
-      </c>
-      <c r="U19">
-        <v>3.93</v>
-      </c>
-      <c r="V19">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P20" s="1">
         <v>0.2</v>
       </c>
       <c r="Q20" t="s">
-        <v>28</v>
-      </c>
-      <c r="R20">
+        <v>29</v>
+      </c>
+      <c r="S20">
         <v>1</v>
       </c>
-      <c r="S20">
+      <c r="T20">
         <v>4</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <v>0</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>5</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2544,66 +2550,66 @@
         <v>0.2</v>
       </c>
       <c r="Q21" t="s">
-        <v>28</v>
-      </c>
-      <c r="R21" t="s">
+        <v>29</v>
+      </c>
+      <c r="S21" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21">
+        <v>4</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="s">
         <v>25</v>
       </c>
-      <c r="S21">
-        <v>4</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>5</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D22" t="s">
-        <v>24</v>
-      </c>
       <c r="E22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K22" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2612,134 +2618,134 @@
         <v>0.2</v>
       </c>
       <c r="Q22" t="s">
-        <v>28</v>
-      </c>
-      <c r="R22" t="s">
+        <v>29</v>
+      </c>
+      <c r="S22" t="s">
+        <v>26</v>
+      </c>
+      <c r="T22">
+        <v>4</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>5</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" t="s">
         <v>25</v>
       </c>
-      <c r="S22">
-        <v>4</v>
-      </c>
-      <c r="T22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>5</v>
-      </c>
-      <c r="V22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>24</v>
-      </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I23" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P23" s="1">
         <v>0.19600000000000001</v>
       </c>
       <c r="Q23" t="s">
-        <v>28</v>
-      </c>
-      <c r="R23">
+        <v>29</v>
+      </c>
+      <c r="S23">
         <v>1</v>
       </c>
-      <c r="S23">
+      <c r="T23">
         <v>4</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <v>0.5</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>4</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H24" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J24" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O24">
         <v>46</v>
@@ -2748,66 +2754,66 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q24" t="s">
-        <v>28</v>
-      </c>
-      <c r="R24" t="s">
+        <v>29</v>
+      </c>
+      <c r="S24" t="s">
+        <v>26</v>
+      </c>
+      <c r="T24">
+        <v>4</v>
+      </c>
+      <c r="U24">
+        <v>0.5</v>
+      </c>
+      <c r="V24">
+        <v>4</v>
+      </c>
+      <c r="W24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" t="s">
         <v>25</v>
       </c>
-      <c r="S24">
-        <v>4</v>
-      </c>
-      <c r="T24">
-        <v>0.5</v>
-      </c>
-      <c r="U24">
-        <v>4</v>
-      </c>
-      <c r="V24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" t="s">
-        <v>36</v>
-      </c>
-      <c r="D25" t="s">
-        <v>24</v>
-      </c>
       <c r="E25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H25" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L25" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O25">
         <v>46</v>
@@ -2816,131 +2822,131 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q25" t="s">
-        <v>28</v>
-      </c>
-      <c r="R25" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25" t="s">
+        <v>26</v>
+      </c>
+      <c r="T25">
+        <v>4</v>
+      </c>
+      <c r="U25">
+        <v>0.5</v>
+      </c>
+      <c r="V25">
+        <v>4</v>
+      </c>
+      <c r="W25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>24</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
         <v>25</v>
       </c>
-      <c r="S25">
-        <v>4</v>
-      </c>
-      <c r="T25">
-        <v>0.5</v>
-      </c>
-      <c r="U25">
-        <v>4</v>
-      </c>
-      <c r="V25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" t="s">
-        <v>24</v>
-      </c>
       <c r="E26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F26" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P26" s="1">
         <v>1</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>1</v>
       </c>
-      <c r="S26">
+      <c r="T26">
         <v>4.67</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <v>0.57999999999999996</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>4.67</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H27" t="s">
+        <v>67</v>
+      </c>
+      <c r="I27" t="s">
         <v>66</v>
       </c>
-      <c r="I27" t="s">
-        <v>65</v>
-      </c>
       <c r="J27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N27" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -2948,64 +2954,64 @@
       <c r="P27" s="1">
         <v>1</v>
       </c>
-      <c r="R27" t="s">
+      <c r="S27" t="s">
+        <v>26</v>
+      </c>
+      <c r="T27">
+        <v>4.67</v>
+      </c>
+      <c r="U27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="V27">
+        <v>4.67</v>
+      </c>
+      <c r="W27">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C28" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" t="s">
         <v>25</v>
       </c>
-      <c r="S27">
-        <v>4.67</v>
-      </c>
-      <c r="T27">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="U27">
-        <v>4.67</v>
-      </c>
-      <c r="V27">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>22</v>
-      </c>
-      <c r="B28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" t="s">
-        <v>24</v>
-      </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H28" t="s">
+        <v>67</v>
+      </c>
+      <c r="I28" t="s">
         <v>66</v>
       </c>
-      <c r="I28" t="s">
-        <v>65</v>
-      </c>
       <c r="J28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K28" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M28" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O28">
         <v>3</v>
@@ -3013,132 +3019,132 @@
       <c r="P28" s="1">
         <v>1</v>
       </c>
-      <c r="R28" t="s">
+      <c r="S28" t="s">
+        <v>26</v>
+      </c>
+      <c r="T28">
+        <v>4.67</v>
+      </c>
+      <c r="U28">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="V28">
+        <v>4.67</v>
+      </c>
+      <c r="W28">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" t="s">
         <v>25</v>
       </c>
-      <c r="S28">
-        <v>4.67</v>
-      </c>
-      <c r="T28">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="U28">
-        <v>4.67</v>
-      </c>
-      <c r="V28">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="E29" t="s">
         <v>32</v>
       </c>
-      <c r="D29" t="s">
-        <v>24</v>
-      </c>
-      <c r="E29" t="s">
-        <v>31</v>
-      </c>
       <c r="F29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G29">
         <v>1900</v>
       </c>
       <c r="H29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O29" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P29" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q29" t="s">
-        <v>28</v>
-      </c>
-      <c r="R29">
+        <v>29</v>
+      </c>
+      <c r="S29">
         <v>1</v>
       </c>
-      <c r="S29">
+      <c r="T29">
         <v>4.3600000000000003</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <v>1.03</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>3.73</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>1.27</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G30">
         <v>1900</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O30">
         <v>20</v>
@@ -3147,66 +3153,66 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q30" t="s">
-        <v>28</v>
-      </c>
-      <c r="R30" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" t="s">
+        <v>26</v>
+      </c>
+      <c r="T30">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="U30">
+        <v>1.03</v>
+      </c>
+      <c r="V30">
+        <v>3.73</v>
+      </c>
+      <c r="W30">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" t="s">
         <v>25</v>
       </c>
-      <c r="S30">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="T30">
-        <v>1.03</v>
-      </c>
-      <c r="U30">
-        <v>3.73</v>
-      </c>
-      <c r="V30">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>36</v>
-      </c>
-      <c r="D31" t="s">
-        <v>24</v>
-      </c>
       <c r="E31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G31">
         <v>1900</v>
       </c>
       <c r="H31" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31" t="s">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s">
+        <v>26</v>
+      </c>
+      <c r="L31" t="s">
+        <v>74</v>
+      </c>
+      <c r="M31" t="s">
+        <v>70</v>
+      </c>
+      <c r="N31" t="s">
         <v>71</v>
-      </c>
-      <c r="J31" t="s">
-        <v>72</v>
-      </c>
-      <c r="K31" t="s">
-        <v>25</v>
-      </c>
-      <c r="L31" t="s">
-        <v>73</v>
-      </c>
-      <c r="M31" t="s">
-        <v>69</v>
-      </c>
-      <c r="N31" t="s">
-        <v>70</v>
       </c>
       <c r="O31">
         <v>20</v>
@@ -3215,131 +3221,131 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q31" t="s">
-        <v>28</v>
-      </c>
-      <c r="R31" t="s">
+        <v>29</v>
+      </c>
+      <c r="S31" t="s">
+        <v>26</v>
+      </c>
+      <c r="T31">
+        <v>4.3600000000000003</v>
+      </c>
+      <c r="U31">
+        <v>1.03</v>
+      </c>
+      <c r="V31">
+        <v>3.73</v>
+      </c>
+      <c r="W31">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" t="s">
         <v>25</v>
       </c>
-      <c r="S31">
-        <v>4.3600000000000003</v>
-      </c>
-      <c r="T31">
-        <v>1.03</v>
-      </c>
-      <c r="U31">
-        <v>3.73</v>
-      </c>
-      <c r="V31">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>22</v>
-      </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>32</v>
       </c>
-      <c r="D32" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
-      </c>
       <c r="F32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O32" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P32" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>1</v>
       </c>
-      <c r="S32">
+      <c r="T32">
         <v>4.0599999999999996</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <v>1</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>4.13</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I33" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J33" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O33">
         <v>19</v>
@@ -3347,64 +3353,64 @@
       <c r="P33" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="R33" t="s">
+      <c r="S33" t="s">
+        <v>26</v>
+      </c>
+      <c r="T33">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="U33">
+        <v>1</v>
+      </c>
+      <c r="V33">
+        <v>4.13</v>
+      </c>
+      <c r="W33">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" t="s">
         <v>25</v>
       </c>
-      <c r="S33">
-        <v>4.0599999999999996</v>
-      </c>
-      <c r="T33">
-        <v>1</v>
-      </c>
-      <c r="U33">
-        <v>4.13</v>
-      </c>
-      <c r="V33">
-        <v>1.0900000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34" t="s">
-        <v>36</v>
-      </c>
-      <c r="D34" t="s">
-        <v>24</v>
-      </c>
       <c r="E34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F34" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I34" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J34" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K34" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O34">
         <v>19</v>
@@ -3412,65 +3418,65 @@
       <c r="P34" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="R34" t="s">
-        <v>25</v>
-      </c>
-      <c r="S34">
+      <c r="S34" t="s">
+        <v>26</v>
+      </c>
+      <c r="T34">
         <v>4.0599999999999996</v>
       </c>
-      <c r="T34">
+      <c r="U34">
         <v>1</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>4.13</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
-        <v>46082</v>
+        <v>46094</v>
       </c>
     </row>
   </sheetData>
@@ -3748,7 +3754,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85228DDE-C556-480B-A8EE-634E9DB6BA7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94EB6771-EBF2-4095-8608-BAF608EF5E73}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
@@ -3756,7 +3762,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EC5CE1B-1BD6-4316-80DD-7CA3CEA4748B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77956C45-A364-4CC5-9F9B-FB1B7F26E20E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -3775,7 +3781,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62F3A27C-5630-4178-BF85-500E1091F759}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB78234-E600-41EE-A879-21BDC5B3E432}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>

--- a/eng-w26.xlsx
+++ b/eng-w26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gohkust.sharepoint.com/teams/SEA/Shared Documents/SFQ/2526 Winter/Ken_Draft/File Upload to AQA website/Regen_Mar13/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{5A99AFDF-7AF1-4818-B417-3385FD53B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3789758-9D48-4B29-B4C6-5DED05DD84D0}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{5A99AFDF-7AF1-4818-B417-3385FD53B4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{407EED16-3EA7-432B-A0CD-23B462DF57A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C2C8D75B-5B47-4BFF-BBF0-E60AFD6116EA}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="86">
   <si>
     <t>Academic Year</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Low Response Rate Indicator</t>
-  </si>
-  <si>
-    <t>Response Rate (Adjusted)</t>
   </si>
   <si>
     <t>No. of Sections Evaluated</t>
@@ -1143,10 +1140,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4966C0D6-3632-473C-9624-470A15F4ED59}">
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1213,451 +1210,448 @@
       <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>0.253</v>
       </c>
       <c r="Q2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2">
+        <v>9</v>
+      </c>
+      <c r="S2">
+        <v>4.12</v>
+      </c>
+      <c r="T2">
+        <v>0.88</v>
+      </c>
+      <c r="U2">
+        <v>3.99</v>
+      </c>
+      <c r="V2">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="S2">
-        <v>9</v>
-      </c>
-      <c r="T2">
-        <v>4.12</v>
-      </c>
-      <c r="U2">
-        <v>0.88</v>
-      </c>
-      <c r="V2">
-        <v>3.99</v>
-      </c>
-      <c r="W2">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>28</v>
-      </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P3" s="1">
         <v>0.127</v>
       </c>
       <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>3.78</v>
+      </c>
+      <c r="T3">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U3">
+        <v>3.94</v>
+      </c>
+      <c r="V3">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>29</v>
       </c>
-      <c r="S3">
-        <v>1</v>
-      </c>
-      <c r="T3">
-        <v>3.78</v>
-      </c>
-      <c r="U3">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="V3">
-        <v>3.94</v>
-      </c>
-      <c r="W3">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
-      </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4" s="1">
         <v>0.29199999999999998</v>
       </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
       <c r="S4">
-        <v>5</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="T4">
-        <v>4.2300000000000004</v>
+        <v>0.66</v>
       </c>
       <c r="U4">
-        <v>0.66</v>
+        <v>4</v>
       </c>
       <c r="V4">
-        <v>4</v>
-      </c>
-      <c r="W4">
         <v>0.82</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>25</v>
-      </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P5" s="1">
         <v>1</v>
       </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
       <c r="S5">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T5">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U5">
         <v>4.67</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>0.57999999999999996</v>
       </c>
-      <c r="V5">
-        <v>4.67</v>
-      </c>
-      <c r="W5">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s">
         <v>23</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="1">
         <v>0.69199999999999995</v>
       </c>
+      <c r="R6">
+        <v>2</v>
+      </c>
       <c r="S6">
-        <v>2</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="T6">
-        <v>4.1900000000000004</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>1</v>
+        <v>3.96</v>
       </c>
       <c r="V6">
-        <v>3.96</v>
-      </c>
-      <c r="W6">
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G7">
         <v>2020</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P7" s="1">
         <v>0.127</v>
       </c>
       <c r="Q7" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>3.78</v>
       </c>
       <c r="T7">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U7">
-        <v>1.1200000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="V7">
-        <v>3.94</v>
-      </c>
-      <c r="W7">
         <v>0.88</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
         <v>23</v>
-      </c>
-      <c r="B8" t="s">
-        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8">
         <v>2020</v>
       </c>
       <c r="H8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" t="s">
         <v>35</v>
       </c>
-      <c r="I8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J8" t="s">
-        <v>36</v>
-      </c>
       <c r="K8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8">
         <v>213</v>
@@ -1666,66 +1660,66 @@
         <v>0.127</v>
       </c>
       <c r="Q8" t="s">
-        <v>29</v>
-      </c>
-      <c r="S8" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R8" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8">
+        <v>3.78</v>
       </c>
       <c r="T8">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U8">
-        <v>1.1200000000000001</v>
+        <v>3.94</v>
       </c>
       <c r="V8">
-        <v>3.94</v>
-      </c>
-      <c r="W8">
         <v>0.88</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" t="s">
-        <v>25</v>
-      </c>
       <c r="E9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9">
         <v>2020</v>
       </c>
       <c r="H9" t="s">
+        <v>34</v>
+      </c>
+      <c r="I9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" t="s">
         <v>35</v>
       </c>
-      <c r="I9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" t="s">
-        <v>36</v>
-      </c>
       <c r="K9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" t="s">
         <v>38</v>
       </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>39</v>
-      </c>
-      <c r="N9" t="s">
-        <v>40</v>
       </c>
       <c r="O9">
         <v>213</v>
@@ -1734,66 +1728,66 @@
         <v>0.127</v>
       </c>
       <c r="Q9" t="s">
-        <v>29</v>
-      </c>
-      <c r="S9" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R9" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9">
+        <v>3.78</v>
       </c>
       <c r="T9">
-        <v>3.78</v>
+        <v>1.1200000000000001</v>
       </c>
       <c r="U9">
-        <v>1.1200000000000001</v>
+        <v>3.89</v>
       </c>
       <c r="V9">
-        <v>3.89</v>
-      </c>
-      <c r="W9">
         <v>1.01</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
         <v>23</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
         <v>24</v>
       </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>25</v>
-      </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G10">
         <v>2020</v>
       </c>
       <c r="H10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" t="s">
-        <v>36</v>
-      </c>
       <c r="K10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M10" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" t="s">
         <v>41</v>
-      </c>
-      <c r="N10" t="s">
-        <v>42</v>
       </c>
       <c r="O10">
         <v>213</v>
@@ -1802,134 +1796,134 @@
         <v>0.127</v>
       </c>
       <c r="Q10" t="s">
+        <v>28</v>
+      </c>
+      <c r="R10" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10">
+        <v>3.78</v>
+      </c>
+      <c r="T10">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="U10">
+        <v>4</v>
+      </c>
+      <c r="V10">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="S10" t="s">
-        <v>26</v>
-      </c>
-      <c r="T10">
-        <v>3.78</v>
-      </c>
-      <c r="U10">
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="V10">
-        <v>4</v>
-      </c>
-      <c r="W10">
-        <v>0.73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11">
         <v>1028</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P11" s="1">
         <v>0.30599999999999999</v>
       </c>
       <c r="Q11" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R11">
+        <v>1</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>4.07</v>
       </c>
       <c r="T11">
-        <v>4.07</v>
+        <v>0.7</v>
       </c>
       <c r="U11">
-        <v>0.7</v>
+        <v>3.87</v>
       </c>
       <c r="V11">
-        <v>3.87</v>
-      </c>
-      <c r="W11">
         <v>0.92</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
         <v>23</v>
-      </c>
-      <c r="B12" t="s">
-        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G12">
         <v>1028</v>
       </c>
       <c r="H12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" t="s">
+        <v>42</v>
+      </c>
+      <c r="J12" t="s">
         <v>44</v>
       </c>
-      <c r="I12" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" t="s">
-        <v>45</v>
-      </c>
       <c r="K12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O12">
         <v>49</v>
@@ -1938,66 +1932,66 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q12" t="s">
+        <v>28</v>
+      </c>
+      <c r="R12" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12">
+        <v>4.07</v>
+      </c>
+      <c r="T12">
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>3.87</v>
+      </c>
+      <c r="V12">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="S12" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12">
-        <v>4.07</v>
-      </c>
-      <c r="U12">
-        <v>0.7</v>
-      </c>
-      <c r="V12">
-        <v>3.87</v>
-      </c>
-      <c r="W12">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" t="s">
-        <v>30</v>
-      </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13">
         <v>1028</v>
       </c>
       <c r="H13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J13" t="s">
         <v>44</v>
       </c>
-      <c r="I13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" t="s">
         <v>45</v>
       </c>
-      <c r="K13" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" t="s">
+      <c r="M13" t="s">
         <v>46</v>
       </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>47</v>
-      </c>
-      <c r="N13" t="s">
-        <v>48</v>
       </c>
       <c r="O13">
         <v>49</v>
@@ -2006,134 +2000,134 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="Q13" t="s">
+        <v>28</v>
+      </c>
+      <c r="R13" t="s">
+        <v>25</v>
+      </c>
+      <c r="S13">
+        <v>4.07</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>3.87</v>
+      </c>
+      <c r="V13">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" t="s">
         <v>29</v>
       </c>
-      <c r="S13" t="s">
-        <v>26</v>
-      </c>
-      <c r="T13">
-        <v>4.07</v>
-      </c>
-      <c r="U13">
-        <v>0.7</v>
-      </c>
-      <c r="V13">
-        <v>3.87</v>
-      </c>
-      <c r="W13">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" t="s">
-        <v>30</v>
-      </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
         <v>49</v>
       </c>
-      <c r="H14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I14" t="s">
-        <v>50</v>
-      </c>
       <c r="J14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P14" s="1">
         <v>0.34</v>
       </c>
       <c r="Q14" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R14">
+        <v>1</v>
       </c>
       <c r="S14">
-        <v>1</v>
+        <v>4.47</v>
       </c>
       <c r="T14">
-        <v>4.47</v>
+        <v>0.72</v>
       </c>
       <c r="U14">
-        <v>0.72</v>
+        <v>4.12</v>
       </c>
       <c r="V14">
-        <v>4.12</v>
-      </c>
-      <c r="W14">
         <v>0.86</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
         <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I15" t="s">
         <v>49</v>
       </c>
-      <c r="H15" t="s">
-        <v>35</v>
-      </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>50</v>
       </c>
-      <c r="J15" t="s">
-        <v>51</v>
-      </c>
       <c r="K15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O15">
         <v>50</v>
@@ -2142,66 +2136,66 @@
         <v>0.34</v>
       </c>
       <c r="Q15" t="s">
+        <v>28</v>
+      </c>
+      <c r="R15" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15">
+        <v>4.47</v>
+      </c>
+      <c r="T15">
+        <v>0.72</v>
+      </c>
+      <c r="U15">
+        <v>4.12</v>
+      </c>
+      <c r="V15">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" t="s">
         <v>29</v>
       </c>
-      <c r="S15" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15">
-        <v>4.47</v>
-      </c>
-      <c r="U15">
-        <v>0.72</v>
-      </c>
-      <c r="V15">
-        <v>4.12</v>
-      </c>
-      <c r="W15">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" t="s">
-        <v>30</v>
-      </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I16" t="s">
         <v>49</v>
       </c>
-      <c r="H16" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="J16" t="s">
         <v>50</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" t="s">
         <v>51</v>
       </c>
-      <c r="K16" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" t="s">
-        <v>52</v>
-      </c>
       <c r="M16" t="s">
+        <v>46</v>
+      </c>
+      <c r="N16" t="s">
         <v>47</v>
-      </c>
-      <c r="N16" t="s">
-        <v>48</v>
       </c>
       <c r="O16">
         <v>50</v>
@@ -2210,134 +2204,134 @@
         <v>0.34</v>
       </c>
       <c r="Q16" t="s">
+        <v>28</v>
+      </c>
+      <c r="R16" t="s">
+        <v>25</v>
+      </c>
+      <c r="S16">
+        <v>4.47</v>
+      </c>
+      <c r="T16">
+        <v>0.72</v>
+      </c>
+      <c r="U16">
+        <v>4.12</v>
+      </c>
+      <c r="V16">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" t="s">
         <v>29</v>
       </c>
-      <c r="S16" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16">
-        <v>4.47</v>
-      </c>
-      <c r="U16">
-        <v>0.72</v>
-      </c>
-      <c r="V16">
-        <v>4.12</v>
-      </c>
-      <c r="W16">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B17" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" t="s">
-        <v>30</v>
-      </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="s">
+        <v>52</v>
+      </c>
+      <c r="H17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" t="s">
         <v>53</v>
       </c>
-      <c r="H17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I17" t="s">
-        <v>54</v>
-      </c>
       <c r="J17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" s="1">
         <v>0.33300000000000002</v>
       </c>
       <c r="Q17" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R17">
+        <v>1</v>
       </c>
       <c r="S17">
-        <v>1</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="T17">
-        <v>4.2699999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="U17">
-        <v>0.59</v>
+        <v>3.93</v>
       </c>
       <c r="V17">
-        <v>3.93</v>
-      </c>
-      <c r="W17">
         <v>0.88</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
         <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" t="s">
         <v>53</v>
       </c>
-      <c r="H18" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="J18" t="s">
         <v>54</v>
       </c>
-      <c r="J18" t="s">
-        <v>55</v>
-      </c>
       <c r="K18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O18">
         <v>45</v>
@@ -2346,66 +2340,66 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q18" t="s">
+        <v>28</v>
+      </c>
+      <c r="R18" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="T18">
+        <v>0.59</v>
+      </c>
+      <c r="U18">
+        <v>3.93</v>
+      </c>
+      <c r="V18">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" t="s">
         <v>29</v>
       </c>
-      <c r="S18" t="s">
-        <v>26</v>
-      </c>
-      <c r="T18">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U18">
-        <v>0.59</v>
-      </c>
-      <c r="V18">
-        <v>3.93</v>
-      </c>
-      <c r="W18">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" t="s">
-        <v>30</v>
-      </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H19" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" t="s">
         <v>53</v>
       </c>
-      <c r="H19" t="s">
-        <v>35</v>
-      </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>54</v>
       </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" t="s">
         <v>55</v>
       </c>
-      <c r="K19" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" t="s">
-        <v>56</v>
-      </c>
       <c r="M19" t="s">
+        <v>46</v>
+      </c>
+      <c r="N19" t="s">
         <v>47</v>
-      </c>
-      <c r="N19" t="s">
-        <v>48</v>
       </c>
       <c r="O19">
         <v>45</v>
@@ -2414,134 +2408,134 @@
         <v>0.33300000000000002</v>
       </c>
       <c r="Q19" t="s">
+        <v>28</v>
+      </c>
+      <c r="R19" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="T19">
+        <v>0.59</v>
+      </c>
+      <c r="U19">
+        <v>3.93</v>
+      </c>
+      <c r="V19">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" t="s">
         <v>29</v>
       </c>
-      <c r="S19" t="s">
-        <v>26</v>
-      </c>
-      <c r="T19">
-        <v>4.2699999999999996</v>
-      </c>
-      <c r="U19">
-        <v>0.59</v>
-      </c>
-      <c r="V19">
-        <v>3.93</v>
-      </c>
-      <c r="W19">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" t="s">
-        <v>30</v>
-      </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G20" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" t="s">
         <v>57</v>
       </c>
-      <c r="H20" t="s">
-        <v>26</v>
-      </c>
-      <c r="I20" t="s">
-        <v>58</v>
-      </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P20" s="1">
         <v>0.2</v>
       </c>
       <c r="Q20" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R20">
+        <v>1</v>
       </c>
       <c r="S20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T20">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U20">
+        <v>5</v>
+      </c>
+      <c r="V20">
         <v>0</v>
       </c>
-      <c r="V20">
-        <v>5</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
         <v>23</v>
-      </c>
-      <c r="B21" t="s">
-        <v>24</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" t="s">
         <v>57</v>
       </c>
-      <c r="H21" t="s">
-        <v>35</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>58</v>
       </c>
-      <c r="J21" t="s">
-        <v>59</v>
-      </c>
       <c r="K21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O21">
         <v>5</v>
@@ -2550,66 +2544,66 @@
         <v>0.2</v>
       </c>
       <c r="Q21" t="s">
+        <v>28</v>
+      </c>
+      <c r="R21" t="s">
+        <v>25</v>
+      </c>
+      <c r="S21">
+        <v>4</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>5</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" t="s">
         <v>29</v>
       </c>
-      <c r="S21" t="s">
-        <v>26</v>
-      </c>
-      <c r="T21">
-        <v>4</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>5</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" t="s">
-        <v>30</v>
-      </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G22" t="s">
+        <v>56</v>
+      </c>
+      <c r="H22" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" t="s">
         <v>57</v>
       </c>
-      <c r="H22" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>58</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" t="s">
         <v>59</v>
       </c>
-      <c r="K22" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" t="s">
-        <v>60</v>
-      </c>
       <c r="M22" t="s">
+        <v>46</v>
+      </c>
+      <c r="N22" t="s">
         <v>47</v>
-      </c>
-      <c r="N22" t="s">
-        <v>48</v>
       </c>
       <c r="O22">
         <v>5</v>
@@ -2618,134 +2612,134 @@
         <v>0.2</v>
       </c>
       <c r="Q22" t="s">
+        <v>28</v>
+      </c>
+      <c r="R22" t="s">
+        <v>25</v>
+      </c>
+      <c r="S22">
+        <v>4</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>5</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
         <v>29</v>
       </c>
-      <c r="S22" t="s">
-        <v>26</v>
-      </c>
-      <c r="T22">
-        <v>4</v>
-      </c>
-      <c r="U22">
-        <v>0</v>
-      </c>
-      <c r="V22">
-        <v>5</v>
-      </c>
-      <c r="W22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" t="s">
-        <v>30</v>
-      </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G23" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" t="s">
+        <v>25</v>
+      </c>
+      <c r="I23" t="s">
         <v>61</v>
       </c>
-      <c r="H23" t="s">
-        <v>26</v>
-      </c>
-      <c r="I23" t="s">
-        <v>62</v>
-      </c>
       <c r="J23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P23" s="1">
         <v>0.19600000000000001</v>
       </c>
       <c r="Q23" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R23">
+        <v>1</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T23">
+        <v>0.5</v>
+      </c>
+      <c r="U23">
         <v>4</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>0.5</v>
       </c>
-      <c r="V23">
-        <v>4</v>
-      </c>
-      <c r="W23">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
         <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G24" t="s">
+        <v>60</v>
+      </c>
+      <c r="H24" t="s">
+        <v>34</v>
+      </c>
+      <c r="I24" t="s">
         <v>61</v>
       </c>
-      <c r="H24" t="s">
-        <v>35</v>
-      </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>62</v>
       </c>
-      <c r="J24" t="s">
-        <v>63</v>
-      </c>
       <c r="K24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N24" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O24">
         <v>46</v>
@@ -2754,66 +2748,66 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q24" t="s">
+        <v>28</v>
+      </c>
+      <c r="R24" t="s">
+        <v>25</v>
+      </c>
+      <c r="S24">
+        <v>4</v>
+      </c>
+      <c r="T24">
+        <v>0.5</v>
+      </c>
+      <c r="U24">
+        <v>4</v>
+      </c>
+      <c r="V24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" t="s">
         <v>29</v>
       </c>
-      <c r="S24" t="s">
-        <v>26</v>
-      </c>
-      <c r="T24">
-        <v>4</v>
-      </c>
-      <c r="U24">
-        <v>0.5</v>
-      </c>
-      <c r="V24">
-        <v>4</v>
-      </c>
-      <c r="W24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" t="s">
-        <v>30</v>
-      </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G25" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" t="s">
+        <v>34</v>
+      </c>
+      <c r="I25" t="s">
         <v>61</v>
       </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>62</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" t="s">
         <v>63</v>
       </c>
-      <c r="K25" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" t="s">
-        <v>64</v>
-      </c>
       <c r="M25" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" t="s">
         <v>47</v>
-      </c>
-      <c r="N25" t="s">
-        <v>48</v>
       </c>
       <c r="O25">
         <v>46</v>
@@ -2822,131 +2816,131 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="Q25" t="s">
-        <v>29</v>
-      </c>
-      <c r="S25" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R25" t="s">
+        <v>25</v>
+      </c>
+      <c r="S25">
+        <v>4</v>
       </c>
       <c r="T25">
+        <v>0.5</v>
+      </c>
+      <c r="U25">
         <v>4</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>0.5</v>
       </c>
-      <c r="V25">
-        <v>4</v>
-      </c>
-      <c r="W25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>22</v>
+      </c>
+      <c r="B26" t="s">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" t="s">
         <v>24</v>
       </c>
-      <c r="C26" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" t="s">
-        <v>25</v>
-      </c>
       <c r="E26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G26" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" t="s">
         <v>65</v>
       </c>
-      <c r="H26" t="s">
-        <v>26</v>
-      </c>
-      <c r="I26" t="s">
-        <v>66</v>
-      </c>
       <c r="J26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P26" s="1">
         <v>1</v>
       </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
       <c r="S26">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="T26">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U26">
         <v>4.67</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>0.57999999999999996</v>
       </c>
-      <c r="V26">
-        <v>4.67</v>
-      </c>
-      <c r="W26">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" t="s">
         <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>24</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G27" t="s">
+        <v>64</v>
+      </c>
+      <c r="H27" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" t="s">
         <v>65</v>
       </c>
-      <c r="H27" t="s">
+      <c r="J27" t="s">
         <v>67</v>
       </c>
-      <c r="I27" t="s">
-        <v>66</v>
-      </c>
-      <c r="J27" t="s">
-        <v>68</v>
-      </c>
       <c r="K27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O27">
         <v>3</v>
@@ -2954,64 +2948,64 @@
       <c r="P27" s="1">
         <v>1</v>
       </c>
-      <c r="S27" t="s">
-        <v>26</v>
+      <c r="R27" t="s">
+        <v>25</v>
+      </c>
+      <c r="S27">
+        <v>4.67</v>
       </c>
       <c r="T27">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U27">
         <v>4.67</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>0.57999999999999996</v>
       </c>
-      <c r="V27">
-        <v>4.67</v>
-      </c>
-      <c r="W27">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" t="s">
         <v>23</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
         <v>24</v>
       </c>
-      <c r="C28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" t="s">
-        <v>25</v>
-      </c>
       <c r="E28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G28" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" t="s">
         <v>65</v>
       </c>
-      <c r="H28" t="s">
+      <c r="J28" t="s">
         <v>67</v>
       </c>
-      <c r="I28" t="s">
-        <v>66</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" t="s">
         <v>68</v>
       </c>
-      <c r="K28" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="M28" t="s">
         <v>69</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>70</v>
-      </c>
-      <c r="N28" t="s">
-        <v>71</v>
       </c>
       <c r="O28">
         <v>3</v>
@@ -3019,132 +3013,132 @@
       <c r="P28" s="1">
         <v>1</v>
       </c>
-      <c r="S28" t="s">
-        <v>26</v>
+      <c r="R28" t="s">
+        <v>25</v>
+      </c>
+      <c r="S28">
+        <v>4.67</v>
       </c>
       <c r="T28">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="U28">
         <v>4.67</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>0.57999999999999996</v>
       </c>
-      <c r="V28">
-        <v>4.67</v>
-      </c>
-      <c r="W28">
-        <v>0.57999999999999996</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" t="s">
         <v>23</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" t="s">
         <v>24</v>
       </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>25</v>
-      </c>
       <c r="E29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29">
         <v>1900</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P29" s="1">
         <v>0.55000000000000004</v>
       </c>
       <c r="Q29" t="s">
-        <v>29</v>
+        <v>28</v>
+      </c>
+      <c r="R29">
+        <v>1</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="T29">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
       </c>
       <c r="U29">
-        <v>1.03</v>
+        <v>3.73</v>
       </c>
       <c r="V29">
-        <v>3.73</v>
-      </c>
-      <c r="W29">
         <v>1.27</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
         <v>23</v>
-      </c>
-      <c r="B30" t="s">
-        <v>24</v>
       </c>
       <c r="C30" t="s">
         <v>7</v>
       </c>
       <c r="D30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G30">
         <v>1900</v>
       </c>
       <c r="H30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
+        <v>71</v>
+      </c>
+      <c r="J30" t="s">
         <v>72</v>
       </c>
-      <c r="J30" t="s">
-        <v>73</v>
-      </c>
       <c r="K30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O30">
         <v>20</v>
@@ -3153,66 +3147,66 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q30" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R30" t="s">
+        <v>25</v>
+      </c>
+      <c r="S30">
+        <v>4.3600000000000003</v>
       </c>
       <c r="T30">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
       </c>
       <c r="U30">
-        <v>1.03</v>
+        <v>3.73</v>
       </c>
       <c r="V30">
-        <v>3.73</v>
-      </c>
-      <c r="W30">
         <v>1.27</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" t="s">
         <v>23</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31" t="s">
         <v>24</v>
       </c>
-      <c r="C31" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" t="s">
-        <v>25</v>
-      </c>
       <c r="E31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G31">
         <v>1900</v>
       </c>
       <c r="H31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I31" t="s">
+        <v>71</v>
+      </c>
+      <c r="J31" t="s">
         <v>72</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" t="s">
         <v>73</v>
       </c>
-      <c r="K31" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" t="s">
-        <v>74</v>
-      </c>
       <c r="M31" t="s">
+        <v>69</v>
+      </c>
+      <c r="N31" t="s">
         <v>70</v>
-      </c>
-      <c r="N31" t="s">
-        <v>71</v>
       </c>
       <c r="O31">
         <v>20</v>
@@ -3221,131 +3215,131 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="Q31" t="s">
-        <v>29</v>
-      </c>
-      <c r="S31" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="R31" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31">
+        <v>4.3600000000000003</v>
       </c>
       <c r="T31">
-        <v>4.3600000000000003</v>
+        <v>1.03</v>
       </c>
       <c r="U31">
-        <v>1.03</v>
+        <v>3.73</v>
       </c>
       <c r="V31">
-        <v>3.73</v>
-      </c>
-      <c r="W31">
         <v>1.27</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>22</v>
+      </c>
+      <c r="B32" t="s">
         <v>23</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" t="s">
         <v>24</v>
       </c>
-      <c r="C32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" t="s">
-        <v>25</v>
-      </c>
       <c r="E32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G32" t="s">
+        <v>74</v>
+      </c>
+      <c r="H32" t="s">
+        <v>25</v>
+      </c>
+      <c r="I32" t="s">
         <v>75</v>
       </c>
-      <c r="H32" t="s">
-        <v>26</v>
-      </c>
-      <c r="I32" t="s">
-        <v>76</v>
-      </c>
       <c r="J32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O32" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P32" s="1">
         <v>0.84199999999999997</v>
       </c>
+      <c r="R32">
+        <v>1</v>
+      </c>
       <c r="S32">
+        <v>4.0599999999999996</v>
+      </c>
+      <c r="T32">
         <v>1</v>
       </c>
-      <c r="T32">
-        <v>4.0599999999999996</v>
-      </c>
       <c r="U32">
-        <v>1</v>
+        <v>4.13</v>
       </c>
       <c r="V32">
-        <v>4.13</v>
-      </c>
-      <c r="W32">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
         <v>23</v>
-      </c>
-      <c r="B33" t="s">
-        <v>24</v>
       </c>
       <c r="C33" t="s">
         <v>7</v>
       </c>
       <c r="D33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F33" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G33" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" t="s">
         <v>75</v>
       </c>
-      <c r="H33" t="s">
-        <v>35</v>
-      </c>
-      <c r="I33" t="s">
+      <c r="J33" t="s">
         <v>76</v>
       </c>
-      <c r="J33" t="s">
-        <v>77</v>
-      </c>
       <c r="K33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N33" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O33">
         <v>19</v>
@@ -3353,64 +3347,64 @@
       <c r="P33" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="S33" t="s">
-        <v>26</v>
+      <c r="R33" t="s">
+        <v>25</v>
+      </c>
+      <c r="S33">
+        <v>4.0599999999999996</v>
       </c>
       <c r="T33">
-        <v>4.0599999999999996</v>
+        <v>1</v>
       </c>
       <c r="U33">
-        <v>1</v>
+        <v>4.13</v>
       </c>
       <c r="V33">
-        <v>4.13</v>
-      </c>
-      <c r="W33">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" t="s">
         <v>23</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s">
         <v>24</v>
       </c>
-      <c r="C34" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" t="s">
-        <v>25</v>
-      </c>
       <c r="E34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G34" t="s">
+        <v>74</v>
+      </c>
+      <c r="H34" t="s">
+        <v>34</v>
+      </c>
+      <c r="I34" t="s">
         <v>75</v>
       </c>
-      <c r="H34" t="s">
-        <v>35</v>
-      </c>
-      <c r="I34" t="s">
+      <c r="J34" t="s">
         <v>76</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" t="s">
         <v>77</v>
       </c>
-      <c r="K34" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" t="s">
-        <v>78</v>
-      </c>
       <c r="M34" t="s">
+        <v>69</v>
+      </c>
+      <c r="N34" t="s">
         <v>70</v>
-      </c>
-      <c r="N34" t="s">
-        <v>71</v>
       </c>
       <c r="O34">
         <v>19</v>
@@ -3418,63 +3412,63 @@
       <c r="P34" s="1">
         <v>0.84199999999999997</v>
       </c>
-      <c r="S34" t="s">
-        <v>26</v>
+      <c r="R34" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34">
+        <v>4.0599999999999996</v>
       </c>
       <c r="T34">
-        <v>4.0599999999999996</v>
+        <v>1</v>
       </c>
       <c r="U34">
-        <v>1</v>
+        <v>4.13</v>
       </c>
       <c r="V34">
-        <v>4.13</v>
-      </c>
-      <c r="W34">
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>46094</v>
       </c>
@@ -3485,15 +3479,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010064FBF1EC94D9E9419E928C7F04731A98" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d5d1fc6aea0bdb544d42f3777360a695">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="307c76f0-d205-4835-9aae-d70c69349486" xmlns:ns3="c1544048-3019-4d62-a7f3-2ad0cae9f9e9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="91955e799b8657f65baef53610b4215d" ns2:_="" ns3:_="">
     <xsd:import namespace="307c76f0-d205-4835-9aae-d70c69349486"/>
@@ -3742,6 +3727,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3754,14 +3748,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94EB6771-EBF2-4095-8608-BAF608EF5E73}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77956C45-A364-4CC5-9F9B-FB1B7F26E20E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3780,6 +3766,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94EB6771-EBF2-4095-8608-BAF608EF5E73}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFB78234-E600-41EE-A879-21BDC5B3E432}">
   <ds:schemaRefs>
